--- a/StructureDefinition-inera-ehds-condition-diagnosis.xlsx
+++ b/StructureDefinition-inera-ehds-condition-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:52:35+00:00</t>
+    <t>2026-09-30T09:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -693,7 +693,7 @@
     <t>Condition.clinicalStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips|2.0.1}
 </t>
   </si>
   <si>
@@ -786,7 +786,7 @@
     <t>In this profile, Condition represents a health problem of the patient. Therefore one of the category value(s) must be problem-list-item.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/problem-type-uv-ips</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/problem-type-uv-ips|2.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -832,7 +832,7 @@
     <t>Condition.category.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding {http://hl7.org/fhir/uv/ips/StructureDefinition/Coding-uv-ips}
+    <t xml:space="preserve">Coding {http://hl7.org/fhir/uv/ips/StructureDefinition/Coding-uv-ips|2.0.1}
 </t>
   </si>
   <si>
@@ -995,7 +995,7 @@
     <t>translation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {translation|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {translation|5.3.0}
 </t>
   </si>
   <si>
@@ -1117,7 +1117,7 @@
     <t>Coding of the severity with a terminology is preferred, where possible.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-severity</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-severity|4.0.1</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -1154,7 +1154,7 @@
     <t>Code for a clinical problem (or absent/unknown problem) that is selected from SNOMED CT</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/problems-uv-ips</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/problems-uv-ips|2.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1305,7 +1305,7 @@
     <t>Only used if not implicit in code found in Condition.code. If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -2102,7 +2102,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="71.2578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="75.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2117,7 +2117,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.00390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.1875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-inera-ehds-condition-diagnosis.xlsx
+++ b/StructureDefinition-inera-ehds-condition-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:02:48+00:00</t>
+    <t>2026-09-30T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-condition-diagnosis.xlsx
+++ b/StructureDefinition-inera-ehds-condition-diagnosis.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$106</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3585" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4038" uniqueCount="604">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:52:57+00:00</t>
+    <t>2026-10-01T18:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -646,6 +646,198 @@
 </t>
   </si>
   <si>
+    <t>Condition.extension:chronicDiagnosis</t>
+  </si>
+  <si>
+    <t>chronicDiagnosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.inera.se/ig/ehds-tk/StructureDefinition/condition-chronic-diagnosis}
+</t>
+  </si>
+  <si>
+    <t>Kronisk diagnos (diagnosisBody.chronicDiagnosis) – se DIAG-001</t>
+  </si>
+  <si>
+    <t>Anger om diagnosen är kronisk (true) eller inte kronisk (false) (diagnosisBody.chronicDiagnosis). Se DIAG-001.</t>
+  </si>
+  <si>
+    <t>Condition.extension:relatedCondition</t>
+  </si>
+  <si>
+    <t>relatedCondition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {condition-related}
+</t>
+  </si>
+  <si>
+    <t>Relaterad diagnos (diagnosisBody.relatedDiagnosis.documentId) – logisk referens via identifier, se DIAG-002</t>
+  </si>
+  <si>
+    <t>This condition has an unspecified relationship with another condition.</t>
+  </si>
+  <si>
+    <t>When the relationship is specified, use the more specific extension, such as condition-dueTo, condition-occurredFollowing, or condition-part of.</t>
+  </si>
+  <si>
+    <t>Condition.extension:relatedCondition.id</t>
+  </si>
+  <si>
+    <t>Condition.extension.id</t>
+  </si>
+  <si>
+    <t>Condition.extension:relatedCondition.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension.extension</t>
+  </si>
+  <si>
+    <t>Condition.extension:relatedCondition.url</t>
+  </si>
+  <si>
+    <t>Condition.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/condition-related</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Condition.extension:relatedCondition.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Condition)
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Condition.extension:relatedCondition.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Condition.extension:relatedCondition.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>Condition.extension:relatedCondition.value[x].reference</t>
+  </si>
+  <si>
+    <t>Condition.extension.value[x].reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>Condition.extension:relatedCondition.value[x].type</t>
+  </si>
+  <si>
+    <t>Condition.extension.value[x].type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Condition.extension:relatedCondition.value[x].identifier</t>
+  </si>
+  <si>
+    <t>Condition.extension.value[x].identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Den relaterade diagnosens dokumentid (relatedDiagnosis.documentId) – motsvarar Condition.identifier på den relaterade diagnosen</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Condition.extension:relatedCondition.value[x].display</t>
+  </si>
+  <si>
+    <t>Condition.extension.value[x].display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
     <t>Condition.modifierExtension</t>
   </si>
   <si>
@@ -663,10 +855,6 @@
   </si>
   <si>
     <t>Condition.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
   </si>
   <si>
     <t>External Ids for this condition</t>
@@ -1358,78 +1546,16 @@
     <t>Condition.subject.reference</t>
   </si>
   <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-1
-</t>
-  </si>
-  <si>
     <t>Condition.subject.type</t>
   </si>
   <si>
-    <t>Type the reference refers to (e.g. "Patient")</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
     <t>Condition.subject.identifier</t>
   </si>
   <si>
     <t>Logical reference, when literal reference is not known</t>
   </si>
   <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
     <t>Condition.subject.display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
   </si>
   <si>
     <t>Condition.encounter</t>
@@ -2089,12 +2215,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP94"/>
+  <dimension ref="A1:AP106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.08984375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="35.8671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.90625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.30078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -4295,48 +4421,46 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="D19" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>112</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>79</v>
       </c>
@@ -4384,7 +4508,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4393,7 +4517,7 @@
         <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>120</v>
@@ -4408,7 +4532,7 @@
         <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4417,14 +4541,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>79</v>
       </c>
@@ -4436,29 +4562,27 @@
         <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O20" t="s" s="2">
         <v>212</v>
       </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>79</v>
       </c>
@@ -4506,7 +4630,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4515,36 +4639,36 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP20" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
+      <c r="A21" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4558,26 +4682,24 @@
         <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>217</v>
+        <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>218</v>
+        <v>106</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>79</v>
@@ -4602,13 +4724,13 @@
         <v>79</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>222</v>
+        <v>79</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>223</v>
+        <v>79</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>79</v>
@@ -4626,7 +4748,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4635,36 +4757,36 @@
         <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>224</v>
+        <v>79</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>226</v>
+        <v>79</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>228</v>
+        <v>109</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4675,29 +4797,27 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>112</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>79</v>
@@ -4722,69 +4842,69 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>221</v>
+        <v>79</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>119</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>237</v>
+        <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>225</v>
+        <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>238</v>
+        <v>79</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>240</v>
+        <v>79</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>241</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4795,10 +4915,10 @@
         <v>91</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>79</v>
@@ -4807,16 +4927,16 @@
         <v>79</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>133</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4824,7 +4944,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>79</v>
+        <v>222</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>79</v>
@@ -4842,69 +4962,71 @@
         <v>79</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>246</v>
+        <v>79</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AC23" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>251</v>
+        <v>79</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>79</v>
       </c>
@@ -4916,7 +5038,7 @@
         <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>79</v>
@@ -4925,17 +5047,15 @@
         <v>79</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4960,11 +5080,13 @@
         <v>79</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>246</v>
+        <v>79</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4982,13 +5104,13 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>79</v>
@@ -5000,16 +5122,16 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>251</v>
+        <v>79</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>79</v>
@@ -5017,10 +5139,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5135,10 +5257,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5253,12 +5375,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5266,13 +5388,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>79</v>
@@ -5281,20 +5403,18 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>261</v>
+        <v>105</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>79</v>
       </c>
@@ -5342,16 +5462,16 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>103</v>
@@ -5363,10 +5483,10 @@
         <v>79</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>268</v>
+        <v>190</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -5377,10 +5497,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5400,18 +5520,20 @@
         <v>79</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>106</v>
+        <v>243</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5436,13 +5558,13 @@
         <v>79</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -5460,7 +5582,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>108</v>
+        <v>248</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5472,7 +5594,7 @@
         <v>79</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>79</v>
@@ -5484,7 +5606,7 @@
         <v>79</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>109</v>
+        <v>190</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5493,44 +5615,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>112</v>
+        <v>251</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>113</v>
+        <v>252</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>114</v>
+        <v>253</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>115</v>
+        <v>254</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5568,31 +5690,31 @@
         <v>79</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>119</v>
+        <v>255</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>79</v>
@@ -5604,7 +5726,7 @@
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>109</v>
+        <v>256</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5613,12 +5735,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5626,13 +5748,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>79</v>
@@ -5641,20 +5763,18 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>79</v>
       </c>
@@ -5663,7 +5783,7 @@
         <v>79</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>79</v>
@@ -5702,7 +5822,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5723,10 +5843,10 @@
         <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>282</v>
+        <v>190</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5737,44 +5857,46 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>79</v>
       </c>
@@ -5822,19 +5944,19 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>79</v>
@@ -5843,10 +5965,10 @@
         <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>290</v>
+        <v>190</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5855,12 +5977,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5868,13 +5990,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>79</v>
@@ -5883,17 +6005,19 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>167</v>
+        <v>251</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5942,13 +6066,13 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>79</v>
@@ -5957,30 +6081,30 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>79</v>
+        <v>273</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>297</v>
+        <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5994,27 +6118,27 @@
         <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>105</v>
+        <v>277</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>79</v>
       </c>
@@ -6038,13 +6162,13 @@
         <v>79</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>79</v>
+        <v>281</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
@@ -6062,7 +6186,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6071,36 +6195,36 @@
         <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>79</v>
+        <v>284</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>79</v>
+        <v>286</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6114,24 +6238,26 @@
         <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>105</v>
+        <v>291</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>79</v>
@@ -6156,13 +6282,13 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>79</v>
+        <v>281</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>79</v>
+        <v>295</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>79</v>
+        <v>296</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>79</v>
@@ -6180,7 +6306,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>108</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6189,36 +6315,36 @@
         <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>79</v>
+        <v>297</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>79</v>
+        <v>300</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>79</v>
+        <v>289</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6226,13 +6352,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>79</v>
@@ -6241,15 +6367,17 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>112</v>
+        <v>277</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>192</v>
+        <v>303</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6274,19 +6402,17 @@
         <v>79</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>116</v>
+        <v>307</v>
       </c>
       <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
@@ -6296,7 +6422,7 @@
         <v>118</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>119</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6308,49 +6434,49 @@
         <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>79</v>
+        <v>308</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C36" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>79</v>
@@ -6359,15 +6485,17 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6392,13 +6520,11 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>79</v>
+        <v>306</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -6416,7 +6542,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>119</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6425,25 +6551,25 @@
         <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>79</v>
+        <v>308</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>79</v>
@@ -6451,10 +6577,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6480,10 +6606,10 @@
         <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>321</v>
+        <v>106</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
+        <v>107</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6507,7 +6633,7 @@
         <v>79</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
         <v>79</v>
@@ -6534,7 +6660,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>108</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6558,7 +6684,7 @@
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6569,21 +6695,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>79</v>
@@ -6592,23 +6718,21 @@
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>327</v>
+        <v>112</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>328</v>
+        <v>113</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>329</v>
+        <v>114</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6644,31 +6768,31 @@
         <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>332</v>
+        <v>119</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>79</v>
@@ -6677,10 +6801,10 @@
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>333</v>
+        <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>334</v>
+        <v>109</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6691,10 +6815,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6702,7 +6826,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>91</v>
@@ -6717,19 +6841,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>105</v>
+        <v>321</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6778,13 +6902,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6799,10 +6923,10 @@
         <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6813,10 +6937,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6842,10 +6966,10 @@
         <v>105</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>309</v>
+        <v>106</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>310</v>
+        <v>107</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6920,7 +7044,7 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6931,14 +7055,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6960,12 +7084,14 @@
         <v>112</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>192</v>
+        <v>113</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>79</v>
@@ -7004,7 +7130,9 @@
       <c r="AB41" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AC41" s="2"/>
+      <c r="AC41" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="AD41" t="s" s="2">
         <v>79</v>
       </c>
@@ -7036,7 +7164,7 @@
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -7045,46 +7173,48 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C42" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>315</v>
+        <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
       </c>
@@ -7093,7 +7223,7 @@
         <v>79</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>79</v>
+        <v>339</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>79</v>
@@ -7132,19 +7262,19 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>119</v>
+        <v>340</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
@@ -7153,10 +7283,10 @@
         <v>79</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7167,10 +7297,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7190,18 +7320,20 @@
         <v>79</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -7223,7 +7355,7 @@
         <v>79</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="X43" t="s" s="2">
         <v>79</v>
@@ -7250,7 +7382,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7262,7 +7394,7 @@
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>79</v>
@@ -7271,10 +7403,10 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>79</v>
+        <v>349</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -7288,7 +7420,7 @@
         <v>351</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7296,7 +7428,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>91</v>
@@ -7308,21 +7440,21 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N44" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="O44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
@@ -7346,11 +7478,13 @@
         <v>79</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>79</v>
@@ -7368,7 +7502,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7386,7 +7520,7 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>357</v>
@@ -7395,32 +7529,32 @@
         <v>358</v>
       </c>
       <c r="AO44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP44" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AP44" t="s" s="2">
+      <c r="B45" t="s" s="2">
         <v>360</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>362</v>
+        <v>79</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>79</v>
@@ -7429,17 +7563,17 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>217</v>
+        <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7464,13 +7598,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>171</v>
+        <v>79</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>366</v>
+        <v>79</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>367</v>
+        <v>79</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7488,7 +7622,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7503,30 +7637,30 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>368</v>
+        <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>369</v>
+        <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>372</v>
+        <v>79</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>373</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7552,10 +7686,10 @@
         <v>105</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>106</v>
+        <v>369</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>107</v>
+        <v>370</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7630,7 +7764,7 @@
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7641,14 +7775,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7670,14 +7804,12 @@
         <v>112</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>113</v>
+        <v>192</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7716,9 +7848,7 @@
       <c r="AB47" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AC47" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7750,7 +7880,7 @@
         <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7761,12 +7891,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7778,29 +7910,25 @@
         <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>261</v>
+        <v>375</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>262</v>
+        <v>376</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7836,17 +7964,19 @@
         <v>79</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AC48" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>266</v>
+        <v>119</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7855,10 +7985,10 @@
         <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
@@ -7867,10 +7997,10 @@
         <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>268</v>
+        <v>378</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7879,16 +8009,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>79</v>
       </c>
@@ -7900,29 +8028,25 @@
         <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>261</v>
+        <v>105</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>262</v>
+        <v>381</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
       </c>
@@ -7943,7 +8067,7 @@
         <v>79</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>79</v>
+        <v>383</v>
       </c>
       <c r="X49" t="s" s="2">
         <v>79</v>
@@ -7970,19 +8094,19 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>266</v>
+        <v>384</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
@@ -7991,10 +8115,10 @@
         <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>268</v>
+        <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -8005,10 +8129,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8028,19 +8152,23 @@
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>105</v>
+        <v>387</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>106</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
       </c>
@@ -8088,7 +8216,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>108</v>
+        <v>392</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8100,7 +8228,7 @@
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
@@ -8109,10 +8237,10 @@
         <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>109</v>
+        <v>394</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -8121,46 +8249,48 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>113</v>
+        <v>397</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>114</v>
+        <v>398</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
       </c>
@@ -8196,31 +8326,31 @@
         <v>79</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>119</v>
+        <v>401</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
@@ -8229,10 +8359,10 @@
         <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>79</v>
+        <v>402</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>109</v>
+        <v>403</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8241,12 +8371,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8254,35 +8384,31 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>275</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
       </c>
@@ -8291,7 +8417,7 @@
         <v>79</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>386</v>
+        <v>79</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>79</v>
@@ -8330,7 +8456,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>280</v>
+        <v>108</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8342,7 +8468,7 @@
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -8351,10 +8477,10 @@
         <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>281</v>
+        <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>282</v>
+        <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8365,10 +8491,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8379,7 +8505,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
@@ -8388,20 +8514,18 @@
         <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>285</v>
+        <v>192</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -8438,31 +8562,29 @@
         <v>79</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>288</v>
+        <v>119</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
@@ -8471,10 +8593,10 @@
         <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>289</v>
+        <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>290</v>
+        <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8483,14 +8605,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C54" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="D54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8499,30 +8623,28 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>167</v>
+        <v>375</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>294</v>
+        <v>377</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>295</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8570,19 +8692,19 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>296</v>
+        <v>119</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
@@ -8591,10 +8713,10 @@
         <v>79</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>297</v>
+        <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>298</v>
+        <v>378</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8605,10 +8727,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8628,21 +8750,19 @@
         <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>302</v>
+        <v>382</v>
       </c>
       <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>303</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8663,7 +8783,7 @@
         <v>79</v>
       </c>
       <c r="W55" t="s" s="2">
-        <v>79</v>
+        <v>383</v>
       </c>
       <c r="X55" t="s" s="2">
         <v>79</v>
@@ -8690,7 +8810,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>304</v>
+        <v>384</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8702,7 +8822,7 @@
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
@@ -8711,10 +8831,10 @@
         <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>305</v>
+        <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8723,12 +8843,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8742,7 +8862,7 @@
         <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>79</v>
@@ -8751,15 +8871,17 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>105</v>
+        <v>277</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>309</v>
+        <v>412</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8784,13 +8906,11 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>79</v>
+        <v>415</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8808,7 +8928,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>108</v>
+        <v>411</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8820,65 +8940,67 @@
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>79</v>
+        <v>417</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>79</v>
+        <v>418</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>79</v>
+        <v>419</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>79</v>
+        <v>420</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>79</v>
+        <v>422</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>112</v>
+        <v>277</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>192</v>
+        <v>423</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>193</v>
+        <v>424</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
       </c>
@@ -8902,71 +9024,71 @@
         <v>79</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>79</v>
+        <v>427</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AC57" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>119</v>
+        <v>421</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>79</v>
+        <v>430</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>79</v>
+        <v>431</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>79</v>
+        <v>432</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>79</v>
+        <v>433</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>79</v>
       </c>
@@ -8975,7 +9097,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8987,13 +9109,13 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>315</v>
+        <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>316</v>
+        <v>106</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>317</v>
+        <v>107</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9044,19 +9166,19 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
@@ -9068,7 +9190,7 @@
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>318</v>
+        <v>109</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>
@@ -9079,21 +9201,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>400</v>
+        <v>435</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>79</v>
@@ -9105,15 +9227,17 @@
         <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>321</v>
+        <v>113</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>79</v>
@@ -9135,7 +9259,7 @@
         <v>79</v>
       </c>
       <c r="W59" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
         <v>79</v>
@@ -9150,31 +9274,31 @@
         <v>79</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>324</v>
+        <v>119</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>79</v>
@@ -9186,7 +9310,7 @@
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>79</v>
@@ -9197,10 +9321,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>402</v>
+        <v>436</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9211,10 +9335,10 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>79</v>
@@ -9223,19 +9347,19 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9272,25 +9396,23 @@
         <v>79</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>79</v>
@@ -9305,10 +9427,10 @@
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -9319,12 +9441,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>404</v>
+        <v>438</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>79</v>
       </c>
@@ -9345,19 +9469,19 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>105</v>
+        <v>321</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>405</v>
+        <v>322</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9406,13 +9530,13 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>79</v>
@@ -9427,10 +9551,10 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9441,10 +9565,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>406</v>
+        <v>440</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>406</v>
+        <v>441</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9470,10 +9594,10 @@
         <v>105</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>309</v>
+        <v>106</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>310</v>
+        <v>107</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9548,7 +9672,7 @@
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9559,14 +9683,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>407</v>
+        <v>442</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9588,12 +9712,14 @@
         <v>112</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>192</v>
+        <v>113</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -9632,7 +9758,9 @@
       <c r="AB63" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AC63" s="2"/>
+      <c r="AC63" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="AD63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9664,7 +9792,7 @@
         <v>79</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>79</v>
@@ -9673,46 +9801,48 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>315</v>
+        <v>133</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
       </c>
@@ -9721,7 +9851,7 @@
         <v>79</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>79</v>
+        <v>446</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>79</v>
@@ -9760,19 +9890,19 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>119</v>
+        <v>340</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
@@ -9781,10 +9911,10 @@
         <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>79</v>
@@ -9795,10 +9925,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>409</v>
+        <v>448</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9818,18 +9948,20 @@
         <v>79</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9851,7 +9983,7 @@
         <v>79</v>
       </c>
       <c r="W65" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="X65" t="s" s="2">
         <v>79</v>
@@ -9878,7 +10010,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9890,7 +10022,7 @@
         <v>79</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>79</v>
@@ -9899,10 +10031,10 @@
         <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>79</v>
+        <v>349</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -9911,12 +10043,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>410</v>
+        <v>449</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9927,10 +10059,10 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>79</v>
@@ -9939,18 +10071,18 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>79</v>
       </c>
@@ -9974,11 +10106,13 @@
         <v>79</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z66" t="s" s="2">
-        <v>414</v>
+        <v>79</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>79</v>
@@ -9996,13 +10130,13 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>410</v>
+        <v>356</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>79</v>
@@ -10014,41 +10148,41 @@
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>415</v>
+        <v>79</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>79</v>
+        <v>357</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>416</v>
+        <v>358</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>418</v>
+        <v>453</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>419</v>
+        <v>79</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>79</v>
@@ -10057,17 +10191,17 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>420</v>
+        <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>421</v>
+        <v>454</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>422</v>
+        <v>362</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>423</v>
+        <v>363</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -10116,10 +10250,10 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>418</v>
+        <v>364</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>91</v>
@@ -10131,19 +10265,19 @@
         <v>103</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>424</v>
+        <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>425</v>
+        <v>365</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>426</v>
+        <v>366</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>427</v>
+        <v>79</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>79</v>
@@ -10151,10 +10285,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10180,10 +10314,10 @@
         <v>105</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>106</v>
+        <v>369</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>107</v>
+        <v>370</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10258,7 +10392,7 @@
         <v>79</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>79</v>
@@ -10269,14 +10403,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>429</v>
+        <v>458</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10298,14 +10432,12 @@
         <v>112</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>113</v>
+        <v>192</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -10344,9 +10476,7 @@
       <c r="AB69" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AC69" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="AC69" s="2"/>
       <c r="AD69" t="s" s="2">
         <v>79</v>
       </c>
@@ -10378,7 +10508,7 @@
         <v>79</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>
@@ -10387,45 +10517,45 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>430</v>
+        <v>459</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="D70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>105</v>
+        <v>375</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>431</v>
+        <v>376</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>79</v>
@@ -10474,19 +10604,19 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>434</v>
+        <v>119</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>435</v>
+        <v>201</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
@@ -10498,7 +10628,7 @@
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>190</v>
+        <v>378</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>79</v>
@@ -10509,10 +10639,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10532,20 +10662,18 @@
         <v>79</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>437</v>
+        <v>381</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10567,16 +10695,16 @@
         <v>79</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>79</v>
+        <v>383</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>440</v>
+        <v>79</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>441</v>
+        <v>79</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>79</v>
@@ -10594,7 +10722,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>442</v>
+        <v>384</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10606,7 +10734,7 @@
         <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
@@ -10618,7 +10746,7 @@
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -10629,10 +10757,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10655,18 +10783,20 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>208</v>
+        <v>387</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>444</v>
+        <v>388</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>445</v>
+        <v>389</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
       </c>
@@ -10714,7 +10844,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>447</v>
+        <v>392</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10735,10 +10865,10 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>448</v>
+        <v>394</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10747,12 +10877,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10766,7 +10896,7 @@
         <v>91</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>79</v>
@@ -10778,15 +10908,17 @@
         <v>105</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>451</v>
+        <v>398</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
       </c>
@@ -10834,7 +10966,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>453</v>
+        <v>401</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10855,10 +10987,10 @@
         <v>79</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>79</v>
+        <v>402</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>190</v>
+        <v>403</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -10869,10 +11001,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10892,20 +11024,18 @@
         <v>79</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>455</v>
+        <v>105</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>456</v>
+        <v>369</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -10954,7 +11084,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>454</v>
+        <v>108</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10966,22 +11096,22 @@
         <v>79</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>459</v>
+        <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>460</v>
+        <v>79</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>461</v>
+        <v>79</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>462</v>
+        <v>79</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>79</v>
@@ -10989,10 +11119,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11003,29 +11133,27 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>464</v>
+        <v>112</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>465</v>
+        <v>192</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -11062,58 +11190,58 @@
         <v>79</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>468</v>
+        <v>116</v>
       </c>
       <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>469</v>
+        <v>118</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>463</v>
+        <v>119</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>470</v>
+        <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>471</v>
+        <v>79</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>472</v>
+        <v>79</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>473</v>
+        <v>79</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>475</v>
+        <v>374</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>79</v>
@@ -11123,29 +11251,27 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>476</v>
+        <v>375</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>477</v>
+        <v>376</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>79</v>
@@ -11194,34 +11320,34 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>463</v>
+        <v>119</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>79</v>
+        <v>201</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>470</v>
+        <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>471</v>
+        <v>79</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>472</v>
+        <v>378</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>473</v>
+        <v>79</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>79</v>
@@ -11229,10 +11355,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11255,17 +11381,15 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>464</v>
+        <v>105</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>479</v>
+        <v>381</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>79</v>
@@ -11287,7 +11411,7 @@
         <v>79</v>
       </c>
       <c r="W77" t="s" s="2">
-        <v>79</v>
+        <v>383</v>
       </c>
       <c r="X77" t="s" s="2">
         <v>79</v>
@@ -11314,7 +11438,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>478</v>
+        <v>384</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11323,10 +11447,10 @@
         <v>91</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>482</v>
+        <v>79</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>79</v>
@@ -11338,21 +11462,21 @@
         <v>79</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>483</v>
+        <v>79</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>484</v>
+        <v>79</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11363,10 +11487,10 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>79</v>
@@ -11375,15 +11499,17 @@
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>476</v>
+        <v>291</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -11408,13 +11534,11 @@
         <v>79</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>79</v>
+        <v>474</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>79</v>
@@ -11432,13 +11556,13 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>79</v>
@@ -11450,35 +11574,35 @@
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>79</v>
+        <v>475</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>488</v>
+        <v>79</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>490</v>
+        <v>79</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>79</v>
+        <v>477</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>79</v>
+        <v>479</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>91</v>
@@ -11493,16 +11617,18 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>79</v>
       </c>
@@ -11550,10 +11676,10 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>91</v>
@@ -11565,30 +11691,30 @@
         <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>79</v>
+        <v>484</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>79</v>
+        <v>485</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11602,22 +11728,22 @@
         <v>91</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>492</v>
+        <v>105</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>498</v>
+        <v>106</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>499</v>
+        <v>107</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11668,7 +11794,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>497</v>
+        <v>108</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11680,7 +11806,7 @@
         <v>79</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>79</v>
@@ -11689,13 +11815,13 @@
         <v>79</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>500</v>
+        <v>79</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>501</v>
+        <v>109</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>502</v>
+        <v>79</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>79</v>
@@ -11703,14 +11829,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11729,15 +11855,17 @@
         <v>79</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>504</v>
+        <v>112</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>505</v>
+        <v>113</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>79</v>
@@ -11774,19 +11902,19 @@
         <v>79</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>503</v>
+        <v>119</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11798,7 +11926,7 @@
         <v>79</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>507</v>
+        <v>120</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>79</v>
@@ -11810,7 +11938,7 @@
         <v>79</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>508</v>
+        <v>109</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>79</v>
@@ -11819,12 +11947,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11832,30 +11960,32 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>105</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>106</v>
+        <v>236</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>237</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>79</v>
@@ -11904,7 +12034,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>108</v>
+        <v>239</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -11913,10 +12043,10 @@
         <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>79</v>
@@ -11928,7 +12058,7 @@
         <v>79</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>109</v>
+        <v>190</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>79</v>
@@ -11939,21 +12069,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>79</v>
@@ -11962,19 +12092,19 @@
         <v>79</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>113</v>
+        <v>243</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>114</v>
+        <v>244</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>115</v>
+        <v>245</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12000,13 +12130,13 @@
         <v>79</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>79</v>
@@ -12024,19 +12154,19 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>119</v>
+        <v>248</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>79</v>
@@ -12048,7 +12178,7 @@
         <v>79</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>109</v>
+        <v>190</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>79</v>
@@ -12059,46 +12189,44 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>512</v>
+        <v>79</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J84" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>112</v>
+        <v>251</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>514</v>
+        <v>253</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>79</v>
       </c>
@@ -12146,19 +12274,19 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>515</v>
+        <v>255</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>79</v>
@@ -12170,7 +12298,7 @@
         <v>79</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>190</v>
+        <v>256</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>79</v>
@@ -12181,10 +12309,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>516</v>
+        <v>494</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>516</v>
+        <v>494</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12204,18 +12332,20 @@
         <v>79</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>231</v>
+        <v>105</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>517</v>
+        <v>259</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>79</v>
@@ -12240,13 +12370,13 @@
         <v>79</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>519</v>
+        <v>79</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>520</v>
+        <v>79</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>79</v>
@@ -12264,7 +12394,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>516</v>
+        <v>262</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12273,7 +12403,7 @@
         <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>521</v>
+        <v>79</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>103</v>
@@ -12282,13 +12412,13 @@
         <v>79</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>522</v>
+        <v>79</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>227</v>
+        <v>79</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>371</v>
+        <v>190</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>79</v>
@@ -12299,10 +12429,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>523</v>
+        <v>495</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>523</v>
+        <v>495</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12313,7 +12443,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>79</v>
@@ -12322,18 +12452,20 @@
         <v>79</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>524</v>
+        <v>496</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>525</v>
+        <v>497</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>79</v>
@@ -12382,34 +12514,34 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>523</v>
+        <v>495</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>521</v>
+        <v>79</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>79</v>
+        <v>500</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>79</v>
+        <v>501</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>527</v>
+        <v>502</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>79</v>
+        <v>503</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>79</v>
@@ -12417,10 +12549,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>528</v>
+        <v>504</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>528</v>
+        <v>504</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12434,24 +12566,26 @@
         <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>231</v>
+        <v>505</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>529</v>
+        <v>506</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>79</v>
@@ -12476,31 +12610,29 @@
         <v>79</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>531</v>
+        <v>79</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>532</v>
+        <v>79</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>79</v>
+        <v>510</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>528</v>
+        <v>504</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12515,32 +12647,34 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>79</v>
+        <v>511</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>79</v>
+        <v>512</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>79</v>
+        <v>514</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>534</v>
+        <v>515</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
       </c>
@@ -12549,28 +12683,28 @@
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>536</v>
+        <v>507</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>537</v>
+        <v>508</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12620,34 +12754,34 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>534</v>
+        <v>504</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>538</v>
+        <v>103</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>79</v>
+        <v>511</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>79</v>
+        <v>512</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>539</v>
+        <v>513</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>79</v>
+        <v>514</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>79</v>
@@ -12655,10 +12789,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>540</v>
+        <v>519</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>540</v>
+        <v>519</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12681,15 +12815,17 @@
         <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>105</v>
+        <v>505</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>106</v>
+        <v>520</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>79</v>
@@ -12738,7 +12874,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>108</v>
+        <v>519</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12747,10 +12883,10 @@
         <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>79</v>
+        <v>523</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>79</v>
@@ -12762,54 +12898,52 @@
         <v>79</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>109</v>
+        <v>524</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>79</v>
+        <v>525</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>112</v>
+        <v>517</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>113</v>
+        <v>527</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>115</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>79</v>
@@ -12858,19 +12992,19 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>119</v>
+        <v>526</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>79</v>
@@ -12879,60 +13013,56 @@
         <v>79</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>79</v>
+        <v>529</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>109</v>
+        <v>530</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>79</v>
+        <v>531</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>512</v>
+        <v>79</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J91" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>112</v>
+        <v>533</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>79</v>
       </c>
@@ -12980,19 +13110,19 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>79</v>
@@ -13004,21 +13134,21 @@
         <v>79</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>190</v>
+        <v>536</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>79</v>
+        <v>537</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13029,10 +13159,10 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>79</v>
@@ -13041,13 +13171,13 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>231</v>
+        <v>533</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13074,13 +13204,13 @@
         <v>79</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>546</v>
+        <v>79</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>547</v>
+        <v>79</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>79</v>
@@ -13098,34 +13228,34 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>548</v>
+        <v>79</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>549</v>
+        <v>79</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>79</v>
+        <v>541</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>79</v>
@@ -13133,10 +13263,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13156,16 +13286,16 @@
         <v>79</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13216,7 +13346,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13225,11 +13355,11 @@
         <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="AJ93" t="s" s="2">
-        <v>103</v>
-      </c>
       <c r="AK93" t="s" s="2">
         <v>79</v>
       </c>
@@ -13240,10 +13370,10 @@
         <v>79</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>527</v>
+        <v>549</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>551</v>
+        <v>79</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>79</v>
@@ -13251,10 +13381,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13265,7 +13395,7 @@
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>79</v>
@@ -13277,13 +13407,13 @@
         <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>557</v>
+        <v>105</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>558</v>
+        <v>106</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>559</v>
+        <v>107</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13334,41 +13464,1471 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF96" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AG94" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH94" t="s" s="2">
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
+      <c r="AI96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="AK94" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AN94" t="s" s="2">
+      <c r="AK97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI98" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="AO94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP94" t="s" s="2">
+      <c r="AJ98" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP106" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP94">
+  <autoFilter ref="A1:AP106">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13378,7 +14938,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI93">
+  <conditionalFormatting sqref="A2:AI105">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-inera-ehds-condition-diagnosis.xlsx
+++ b/StructureDefinition-inera-ehds-condition-diagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4038" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4038" uniqueCount="605">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T18:35:17+00:00</t>
+    <t>2026-10-02T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -432,7 +432,7 @@
 </t>
   </si>
   <si>
-    <t>Källsystem HSA-id (diagnosisHeader.sourceSystemHSAId) – urn:oid:1.2.752.129.2.1.4.1#{hsaId}</t>
+    <t>Källsystem HSA-id (diagnosisHeader.sourceSystemHSAId) – https://tjanstekatalogen.inera.se/Endpoint/{hsaId} (GENERAL-005)</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -881,7 +881,7 @@
     <t>Condition.clinicalStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips|2.0.1}
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
 </t>
   </si>
   <si>
@@ -974,7 +974,7 @@
     <t>In this profile, Condition represents a health problem of the patient. Therefore one of the category value(s) must be problem-list-item.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/problem-type-uv-ips|2.0.1</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/problem-type-uv-ips</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -999,7 +999,10 @@
     <t>diagnostyp</t>
   </si>
   <si>
-    <t>Diagnostyp (diagnosisBody.typeOfDiagnosis) – HD (Huvuddiagnos) eller BY (Bidiagnos)</t>
+    <t>Diagnostyp (diagnosisBody.typeOfDiagnosis) – HD (Huvuddiagnos) eller BY (Bidiagnos) från kv_diagnostyp</t>
+  </si>
+  <si>
+    <t>https://fhir.inera.se/ig/ehds-tk/ValueSet/diagnosistype-vs</t>
   </si>
   <si>
     <t>Condition.category:diagnostyp.id</t>
@@ -1020,7 +1023,7 @@
     <t>Condition.category.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding {http://hl7.org/fhir/uv/ips/StructureDefinition/Coding-uv-ips|2.0.1}
+    <t xml:space="preserve">Coding {http://hl7.org/fhir/uv/ips/StructureDefinition/Coding-uv-ips}
 </t>
   </si>
   <si>
@@ -1183,7 +1186,7 @@
     <t>translation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {translation|5.3.0}
+    <t xml:space="preserve">Extension {translation|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -1305,7 +1308,7 @@
     <t>Coding of the severity with a terminology is preferred, where possible.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-severity|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-severity</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -1342,7 +1345,7 @@
     <t>Code for a clinical problem (or absent/unknown problem) that is selected from SNOMED CT</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/problems-uv-ips|2.0.1</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/problems-uv-ips</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1493,7 +1496,7 @@
     <t>Only used if not implicit in code found in Condition.code. If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -2228,7 +2231,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="75.78515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="72.1484375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2243,7 +2246,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.1875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.00390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -6520,11 +6523,11 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>149</v>
+        <v>281</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -6577,10 +6580,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6695,10 +6698,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6815,10 +6818,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6841,19 +6844,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6902,7 +6905,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6923,10 +6926,10 @@
         <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6937,10 +6940,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7055,10 +7058,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7175,10 +7178,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7204,16 +7207,16 @@
         <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -7223,7 +7226,7 @@
         <v>79</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>79</v>
@@ -7262,7 +7265,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7283,10 +7286,10 @@
         <v>79</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>79</v>
@@ -7297,10 +7300,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7326,13 +7329,13 @@
         <v>105</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7382,7 +7385,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7403,10 +7406,10 @@
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -7417,10 +7420,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7446,14 +7449,14 @@
         <v>167</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7502,7 +7505,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7523,10 +7526,10 @@
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7537,10 +7540,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7566,14 +7569,14 @@
         <v>105</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7622,7 +7625,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7643,10 +7646,10 @@
         <v>79</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7657,10 +7660,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7686,10 +7689,10 @@
         <v>105</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7775,10 +7778,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7891,13 +7894,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="B48" t="s" s="2">
-        <v>372</v>
-      </c>
       <c r="C48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>79</v>
@@ -7919,13 +7922,13 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8000,7 +8003,7 @@
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -8011,10 +8014,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8040,10 +8043,10 @@
         <v>105</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8067,7 +8070,7 @@
         <v>79</v>
       </c>
       <c r="W49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="X49" t="s" s="2">
         <v>79</v>
@@ -8094,7 +8097,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8129,10 +8132,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8155,19 +8158,19 @@
         <v>92</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -8216,7 +8219,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8237,10 +8240,10 @@
         <v>79</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -8251,10 +8254,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8280,16 +8283,16 @@
         <v>105</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8338,7 +8341,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8359,10 +8362,10 @@
         <v>79</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8373,10 +8376,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8402,10 +8405,10 @@
         <v>105</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8491,10 +8494,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8607,13 +8610,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="B54" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="C54" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>79</v>
@@ -8635,13 +8638,13 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8716,7 +8719,7 @@
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8727,10 +8730,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8756,10 +8759,10 @@
         <v>105</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8783,7 +8786,7 @@
         <v>79</v>
       </c>
       <c r="W55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="X55" t="s" s="2">
         <v>79</v>
@@ -8810,7 +8813,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8845,10 +8848,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8874,13 +8877,13 @@
         <v>277</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8910,7 +8913,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8928,7 +8931,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8946,31 +8949,31 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8992,14 +8995,14 @@
         <v>277</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -9027,10 +9030,10 @@
         <v>171</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>79</v>
@@ -9048,7 +9051,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9063,30 +9066,30 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9201,10 +9204,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9321,10 +9324,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9347,19 +9350,19 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -9396,7 +9399,7 @@
         <v>79</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
@@ -9406,7 +9409,7 @@
         <v>118</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9427,10 +9430,10 @@
         <v>79</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>79</v>
@@ -9441,13 +9444,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>79</v>
@@ -9469,19 +9472,19 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -9530,7 +9533,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9551,10 +9554,10 @@
         <v>79</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>79</v>
@@ -9565,10 +9568,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9683,10 +9686,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9803,10 +9806,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9832,16 +9835,16 @@
         <v>133</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>79</v>
@@ -9851,7 +9854,7 @@
         <v>79</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>79</v>
@@ -9890,7 +9893,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9911,10 +9914,10 @@
         <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>79</v>
@@ -9925,10 +9928,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9954,13 +9957,13 @@
         <v>105</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10010,7 +10013,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10031,10 +10034,10 @@
         <v>79</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -10045,10 +10048,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10074,14 +10077,14 @@
         <v>167</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -10130,7 +10133,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10151,10 +10154,10 @@
         <v>79</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>79</v>
@@ -10165,10 +10168,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10194,14 +10197,14 @@
         <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -10250,7 +10253,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10271,10 +10274,10 @@
         <v>79</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>79</v>
@@ -10285,10 +10288,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10314,10 +10317,10 @@
         <v>105</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10403,10 +10406,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10519,13 +10522,13 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="B70" t="s" s="2">
-        <v>458</v>
-      </c>
       <c r="C70" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>79</v>
@@ -10547,13 +10550,13 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10628,7 +10631,7 @@
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>79</v>
@@ -10639,10 +10642,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10668,10 +10671,10 @@
         <v>105</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10695,7 +10698,7 @@
         <v>79</v>
       </c>
       <c r="W71" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="X71" t="s" s="2">
         <v>79</v>
@@ -10722,7 +10725,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10757,10 +10760,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10783,19 +10786,19 @@
         <v>92</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -10844,7 +10847,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10865,10 +10868,10 @@
         <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10879,10 +10882,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10908,16 +10911,16 @@
         <v>105</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10966,7 +10969,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10987,10 +10990,10 @@
         <v>79</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>79</v>
@@ -11001,10 +11004,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11030,10 +11033,10 @@
         <v>105</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11119,10 +11122,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11235,13 +11238,13 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="B76" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="C76" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>79</v>
@@ -11263,13 +11266,13 @@
         <v>79</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11344,7 +11347,7 @@
         <v>79</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>79</v>
@@ -11355,10 +11358,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11384,10 +11387,10 @@
         <v>105</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11411,7 +11414,7 @@
         <v>79</v>
       </c>
       <c r="W77" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="X77" t="s" s="2">
         <v>79</v>
@@ -11438,7 +11441,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11473,10 +11476,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11502,13 +11505,13 @@
         <v>291</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11538,7 +11541,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>79</v>
@@ -11556,7 +11559,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11574,31 +11577,31 @@
         <v>79</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11617,17 +11620,17 @@
         <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>79</v>
@@ -11676,7 +11679,7 @@
         <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>91</v>
@@ -11691,19 +11694,19 @@
         <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>79</v>
@@ -11711,10 +11714,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11829,10 +11832,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11949,10 +11952,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12069,10 +12072,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12189,10 +12192,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12218,7 +12221,7 @@
         <v>251</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M84" t="s" s="2">
         <v>253</v>
@@ -12309,10 +12312,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12429,10 +12432,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12455,16 +12458,16 @@
         <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12514,7 +12517,7 @@
         <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12529,19 +12532,19 @@
         <v>103</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>79</v>
@@ -12549,10 +12552,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12575,16 +12578,16 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12622,17 +12625,17 @@
         <v>79</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12647,19 +12650,19 @@
         <v>103</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>79</v>
@@ -12667,13 +12670,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
@@ -12695,16 +12698,16 @@
         <v>92</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12754,7 +12757,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12769,19 +12772,19 @@
         <v>103</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>79</v>
@@ -12789,10 +12792,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12815,16 +12818,16 @@
         <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12874,7 +12877,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12883,7 +12886,7 @@
         <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>103</v>
@@ -12898,10 +12901,10 @@
         <v>79</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>79</v>
@@ -12909,10 +12912,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12935,13 +12938,13 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12992,7 +12995,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13013,13 +13016,13 @@
         <v>79</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>79</v>
@@ -13027,10 +13030,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13053,13 +13056,13 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13110,7 +13113,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13134,10 +13137,10 @@
         <v>79</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>79</v>
@@ -13145,10 +13148,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13171,13 +13174,13 @@
         <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13228,7 +13231,7 @@
         <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13249,13 +13252,13 @@
         <v>79</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>79</v>
@@ -13263,10 +13266,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13289,13 +13292,13 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13346,7 +13349,7 @@
         <v>79</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13358,7 +13361,7 @@
         <v>79</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>79</v>
@@ -13370,7 +13373,7 @@
         <v>79</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>79</v>
@@ -13381,10 +13384,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13499,10 +13502,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13619,14 +13622,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13648,10 +13651,10 @@
         <v>112</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>115</v>
@@ -13706,7 +13709,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13741,10 +13744,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13770,10 +13773,10 @@
         <v>291</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13803,10 +13806,10 @@
         <v>157</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>79</v>
@@ -13824,7 +13827,7 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13833,7 +13836,7 @@
         <v>91</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>103</v>
@@ -13842,13 +13845,13 @@
         <v>79</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>287</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>79</v>
@@ -13859,10 +13862,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13885,13 +13888,13 @@
         <v>79</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13942,7 +13945,7 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13951,7 +13954,7 @@
         <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>103</v>
@@ -13966,7 +13969,7 @@
         <v>79</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>79</v>
@@ -13977,10 +13980,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14006,10 +14009,10 @@
         <v>291</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14039,10 +14042,10 @@
         <v>157</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>79</v>
@@ -14060,7 +14063,7 @@
         <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14084,7 +14087,7 @@
         <v>79</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>79</v>
@@ -14095,10 +14098,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14121,16 +14124,16 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14180,7 +14183,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14192,7 +14195,7 @@
         <v>79</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>79</v>
@@ -14204,7 +14207,7 @@
         <v>79</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>79</v>
@@ -14215,10 +14218,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14333,10 +14336,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14453,14 +14456,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14482,10 +14485,10 @@
         <v>112</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>115</v>
@@ -14540,7 +14543,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14575,10 +14578,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14604,10 +14607,10 @@
         <v>291</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14637,10 +14640,10 @@
         <v>157</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>79</v>
@@ -14658,7 +14661,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14667,13 +14670,13 @@
         <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>308</v>
@@ -14682,10 +14685,10 @@
         <v>79</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AP104" t="s" s="2">
         <v>79</v>
@@ -14693,10 +14696,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14719,13 +14722,13 @@
         <v>92</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14776,7 +14779,7 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14785,7 +14788,7 @@
         <v>81</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>103</v>
@@ -14800,10 +14803,10 @@
         <v>79</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AP105" t="s" s="2">
         <v>79</v>
@@ -14811,10 +14814,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14837,13 +14840,13 @@
         <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14894,7 +14897,7 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14909,16 +14912,16 @@
         <v>103</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>79</v>
